--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356097</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128355612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356479</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356693</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794827</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410012</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128355807</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409981</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356050</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356114</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1773,6 +1828,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356165</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1870,6 +1930,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128355573</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1967,6 +2032,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356578</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2064,6 +2134,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409976</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2171,6 +2246,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356565</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2268,6 +2348,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356582</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2365,6 +2450,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410172</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2462,6 +2552,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128355560</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2559,6 +2654,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128355869</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2683,8 +2783,35 @@
           <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128408258</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128356479</v>
+        <v>136373213</v>
       </c>
       <c r="B4" t="n">
-        <v>87196</v>
+        <v>92887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>427</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartkärret, Upl</t>
+          <t>Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696746</v>
+        <v>696474</v>
       </c>
       <c r="R4" t="n">
-        <v>6649968</v>
+        <v>6649930</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,60 +984,60 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund, Johan Björkstén, Bo Törnquist, Kjell  Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128356479</t>
+          <t>https://artportalen.se/Sighting/136373213</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356693</v>
+        <v>136373236</v>
       </c>
       <c r="B5" t="n">
-        <v>91375</v>
+        <v>92887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>720</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrhenninge, Norrhenninge, Upl</t>
+          <t>Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696639</v>
+        <v>696545</v>
       </c>
       <c r="R5" t="n">
-        <v>6649963</v>
+        <v>6649839</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,68 +1091,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Björkstén, Bo Törnquist, Viktor Lund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128356693</t>
+          <t>https://artportalen.se/Sighting/136373236</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128794827</v>
+        <v>128356479</v>
       </c>
       <c r="B6" t="n">
-        <v>91436</v>
+        <v>87196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1357</v>
+        <v>427</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrhenninge, Upl</t>
+          <t>Svartkärret, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696735</v>
+        <v>696746</v>
       </c>
       <c r="R6" t="n">
-        <v>6649976</v>
+        <v>6649968</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1166,12 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,72 +1187,71 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Viktor Lund, Johan Björkstén, Bo Törnquist, Kjell  Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128794827</t>
+          <t>https://artportalen.se/Sighting/128356479</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128410012</v>
+        <v>128356693</v>
       </c>
       <c r="B7" t="n">
-        <v>92358</v>
+        <v>91375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1619</v>
+        <v>720</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Apelticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aurantiporus fissilis</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svartkärret, Upl</t>
+          <t>Norrhenninge, Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696589</v>
+        <v>696639</v>
       </c>
       <c r="R7" t="n">
-        <v>6649829</v>
+        <v>6649963</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1269,12 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,65 +1305,68 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund, Johan Björkstén</t>
+          <t>Johan Björkstén, Bo Törnquist, Viktor Lund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128410012</t>
+          <t>https://artportalen.se/Sighting/128356693</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128355807</v>
+        <v>128794827</v>
       </c>
       <c r="B8" t="n">
-        <v>96426</v>
+        <v>91436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>1357</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrhenninge, Norrhenninge, Upl</t>
+          <t>Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696571</v>
+        <v>696735</v>
       </c>
       <c r="R8" t="n">
-        <v>6649847</v>
+        <v>6649976</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1371,22 +1390,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,6 +1404,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1406,44 +1416,44 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Björkstén, Bo Törnquist, Viktor Lund</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128355807</t>
+          <t>https://artportalen.se/Sighting/128794827</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128409981</v>
+        <v>128410012</v>
       </c>
       <c r="B9" t="n">
-        <v>96426</v>
+        <v>92358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2671</v>
+        <v>1619</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Apelticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Aurantiporus fissilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696553</v>
+        <v>696589</v>
       </c>
       <c r="R9" t="n">
-        <v>6649832</v>
+        <v>6649829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,16 +1524,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128409981</t>
+          <t>https://artportalen.se/Sighting/128410012</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128356050</v>
+        <v>136373238</v>
       </c>
       <c r="B10" t="n">
-        <v>92497</v>
+        <v>96641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,37 +1541,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3884</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svartkärret, Upl</t>
+          <t>Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696632</v>
+        <v>696550</v>
       </c>
       <c r="R10" t="n">
-        <v>6649911</v>
+        <v>6649823</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1585,12 +1595,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,60 +1635,60 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktor Lund, Johan Björkstén, Bo Törnquist, Kjell  Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128356050</t>
+          <t>https://artportalen.se/Sighting/136373238</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128356114</v>
+        <v>136373245</v>
       </c>
       <c r="B11" t="n">
-        <v>93209</v>
+        <v>96641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svartkärret, Upl</t>
+          <t>Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696634</v>
+        <v>696583</v>
       </c>
       <c r="R11" t="n">
-        <v>6649953</v>
+        <v>6649888</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1687,12 +1712,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1712,44 +1747,44 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Lund, Johan Björkstén, Bo Törnquist, Kjell  Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128356114</t>
+          <t>https://artportalen.se/Sighting/136373245</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128356165</v>
+        <v>128355807</v>
       </c>
       <c r="B12" t="n">
-        <v>93209</v>
+        <v>96426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>2671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,13 +1794,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696639</v>
+        <v>696571</v>
       </c>
       <c r="R12" t="n">
-        <v>6649963</v>
+        <v>6649847</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1804,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,16 +1865,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128356165</t>
+          <t>https://artportalen.se/Sighting/128355807</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128355573</v>
+        <v>128409981</v>
       </c>
       <c r="B13" t="n">
-        <v>91893</v>
+        <v>96426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>2671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696573</v>
+        <v>696553</v>
       </c>
       <c r="R13" t="n">
-        <v>6649814</v>
+        <v>6649832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,12 +1936,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1926,60 +1961,60 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktor Lund, Kjell  Andersson, Bo Törnquist, Johan Björkstén</t>
+          <t>Viktor Lund, Johan Björkstén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128355573</t>
+          <t>https://artportalen.se/Sighting/128409981</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128356578</v>
+        <v>136373237</v>
       </c>
       <c r="B14" t="n">
-        <v>91409</v>
+        <v>96630</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5741</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartkärret, Upl</t>
+          <t>Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696759</v>
+        <v>696545</v>
       </c>
       <c r="R14" t="n">
-        <v>6649960</v>
+        <v>6649839</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2003,12 +2038,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2028,44 +2073,44 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Lund, Johan Björkstén, Bo Törnquist, Kjell  Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128356578</t>
+          <t>https://artportalen.se/Sighting/136373237</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128409976</v>
+        <v>128356050</v>
       </c>
       <c r="B15" t="n">
-        <v>91435</v>
+        <v>92497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5747</v>
+        <v>3884</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2075,13 +2120,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696575</v>
+        <v>696632</v>
       </c>
       <c r="R15" t="n">
-        <v>6649824</v>
+        <v>6649911</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2105,12 +2150,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2130,60 +2175,60 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Lund, Johan Björkstén</t>
+          <t>Viktor Lund, Johan Björkstén, Bo Törnquist, Kjell  Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128409976</t>
+          <t>https://artportalen.se/Sighting/128356050</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128356565</v>
+        <v>136373204</v>
       </c>
       <c r="B16" t="n">
-        <v>91443</v>
+        <v>92648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5754</v>
+        <v>3884</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrhenninge, Norrhenninge, Upl</t>
+          <t>Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696639</v>
+        <v>696636</v>
       </c>
       <c r="R16" t="n">
-        <v>6649963</v>
+        <v>6649912</v>
       </c>
       <c r="S16" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2207,22 +2252,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2237,27 +2282,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Björkstén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Björkstén, Bo Törnquist, Viktor Lund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128356565</t>
+          <t>https://artportalen.se/Sighting/136373204</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128356582</v>
+        <v>128356114</v>
       </c>
       <c r="B17" t="n">
-        <v>102241</v>
+        <v>93209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2289,13 +2334,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696759</v>
+        <v>696634</v>
       </c>
       <c r="R17" t="n">
-        <v>6649960</v>
+        <v>6649953</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2350,16 +2395,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128356582</t>
+          <t>https://artportalen.se/Sighting/128356114</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128410172</v>
+        <v>128356165</v>
       </c>
       <c r="B18" t="n">
-        <v>102241</v>
+        <v>93209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2367,37 +2412,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221235</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartkärret, Upl</t>
+          <t>Norrhenninge, Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696589</v>
+        <v>696639</v>
       </c>
       <c r="R18" t="n">
-        <v>6649829</v>
+        <v>6649963</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2421,12 +2466,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2441,27 +2496,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Johan Björkstén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Lund, Johan Björkstén</t>
+          <t>Johan Björkstén, Bo Törnquist, Viktor Lund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128410172</t>
+          <t>https://artportalen.se/Sighting/128356165</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128355560</v>
+        <v>128355573</v>
       </c>
       <c r="B19" t="n">
-        <v>103683</v>
+        <v>91893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,21 +2524,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222002</v>
+        <v>4660</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2554,16 +2609,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128355560</t>
+          <t>https://artportalen.se/Sighting/128355573</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128355869</v>
+        <v>136373239</v>
       </c>
       <c r="B20" t="n">
-        <v>104628</v>
+        <v>92071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2571,37 +2626,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>4660</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartkärret, Upl</t>
+          <t>Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696554</v>
+        <v>696559</v>
       </c>
       <c r="R20" t="n">
-        <v>6649876</v>
+        <v>6649824</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2625,12 +2680,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2650,63 +2715,60 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktor Lund, Johan Björkstén, Bo Törnquist, Kjell  Andersson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128355869</t>
+          <t>https://artportalen.se/Sighting/136373239</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128408258</v>
+        <v>136373241</v>
       </c>
       <c r="B21" t="n">
-        <v>90733</v>
+        <v>90066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>245031</v>
+        <v>5581</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Gulfotsskölding</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Pluteus romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
+          <t>(Britzelm.) Sacc.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartkärret, Upl</t>
+          <t>Norrhenninge, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696746</v>
+        <v>696554</v>
       </c>
       <c r="R21" t="n">
-        <v>6649968</v>
+        <v>6649839</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2730,17 +2792,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Matchar till 100% identitet med våra tidigare två fynd. Utöver dessa är närmsta match i Unite 96.21% identitet med SJ030827 Tricholoma borgsjoeënse "Larsson,E. and Jacobsson,S.; Description of a new species of Tricholoma; Unpublished ".</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2749,23 +2816,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>barcode</t>
-        </is>
-      </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>F-1217522</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2775,15 +2827,1650 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136373241</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128356578</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91409</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svartkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>696759</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6649960</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Johan Björkstén, Bo Törnquist, Kjell  Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356578</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128409976</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91435</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svartkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>696575</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6649824</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128409976</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128356565</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norrhenninge, Norrhenninge, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>696639</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6649963</v>
+      </c>
+      <c r="S24" t="n">
+        <v>17</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Björkstén, Bo Törnquist, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356565</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136373228</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58154</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norrhenninge, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>696411</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6650087</v>
+      </c>
+      <c r="S25" t="n">
+        <v>7</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136373228</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136373246</v>
+      </c>
+      <c r="B26" t="n">
+        <v>108352</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norrhenninge, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>696616</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6649937</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136373246</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128356582</v>
+      </c>
+      <c r="B27" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svartkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>696759</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6649960</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Johan Björkstén, Bo Törnquist, Kjell  Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356582</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128410172</v>
+      </c>
+      <c r="B28" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svartkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>696589</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6649829</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410172</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136373200</v>
+      </c>
+      <c r="B29" t="n">
+        <v>102453</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norrhenninge, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>696671</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6649927</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136373200</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136373207</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98183</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norrhenninge, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>696659</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6649949</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136373207</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128355560</v>
+      </c>
+      <c r="B31" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svartkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>696573</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6649814</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Kjell  Andersson, Bo Törnquist, Johan Björkstén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128355560</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128355869</v>
+      </c>
+      <c r="B32" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svartkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>696554</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6649876</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Johan Björkstén, Bo Törnquist, Kjell  Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128355869</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136373201</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101537</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Norrhenninge, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>696671</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6649927</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136373201</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136373218</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101439</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Norrhenninge, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>696397</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6650165</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136373218</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136373222</v>
+      </c>
+      <c r="B35" t="n">
+        <v>103622</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norrhenninge, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>696462</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6650156</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Liten planta</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136373222</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128408258</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90733</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>245031</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Borgsjömusseron</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tricholoma borgsjoeënse</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Jacobsson &amp; Muskos</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svartkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>696746</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6649968</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Matchar till 100% identitet med våra tidigare två fynd. Utöver dessa är närmsta match i Unite 96.21% identitet med SJ030827 Tricholoma borgsjoeënse "Larsson,E. and Jacobsson,S.; Description of a new species of Tricholoma; Unpublished ".</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>F-1217522</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
           <t>Viktor Lund, Kristoffer Stighäll, Johan Björkstén</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
+      <c r="AY36" t="inlineStr">
         <is>
           <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128408258</t>
         </is>
@@ -2811,6 +4498,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136373213</v>
       </c>
       <c r="B4" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136373236</v>
       </c>
       <c r="B5" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136373238</v>
       </c>
       <c r="B10" t="n">
-        <v>96641</v>
+        <v>96642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136373245</v>
       </c>
       <c r="B11" t="n">
-        <v>96641</v>
+        <v>96642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>136373237</v>
       </c>
       <c r="B14" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>136373204</v>
       </c>
       <c r="B16" t="n">
-        <v>92648</v>
+        <v>92649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>136373239</v>
       </c>
       <c r="B20" t="n">
-        <v>92071</v>
+        <v>92072</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136373241</v>
       </c>
       <c r="B21" t="n">
-        <v>90066</v>
+        <v>90067</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136373246</v>
       </c>
       <c r="B26" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136373200</v>
       </c>
       <c r="B29" t="n">
-        <v>102453</v>
+        <v>102454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136373207</v>
       </c>
       <c r="B30" t="n">
-        <v>98183</v>
+        <v>98184</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136373201</v>
       </c>
       <c r="B33" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136373218</v>
       </c>
       <c r="B34" t="n">
-        <v>101439</v>
+        <v>101440</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>136373222</v>
       </c>
       <c r="B35" t="n">
-        <v>103622</v>
+        <v>103623</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136373213</v>
       </c>
       <c r="B4" t="n">
-        <v>92888</v>
+        <v>92901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136373236</v>
       </c>
       <c r="B5" t="n">
-        <v>92888</v>
+        <v>92901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136373238</v>
       </c>
       <c r="B10" t="n">
-        <v>96642</v>
+        <v>96655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136373245</v>
       </c>
       <c r="B11" t="n">
-        <v>96642</v>
+        <v>96655</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>136373237</v>
       </c>
       <c r="B14" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>136373204</v>
       </c>
       <c r="B16" t="n">
-        <v>92649</v>
+        <v>92662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>136373239</v>
       </c>
       <c r="B20" t="n">
-        <v>92072</v>
+        <v>92085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136373241</v>
       </c>
       <c r="B21" t="n">
-        <v>90067</v>
+        <v>90080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>136373228</v>
       </c>
       <c r="B25" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136373246</v>
       </c>
       <c r="B26" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136373200</v>
       </c>
       <c r="B29" t="n">
-        <v>102454</v>
+        <v>102467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136373207</v>
       </c>
       <c r="B30" t="n">
-        <v>98184</v>
+        <v>98197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136373201</v>
       </c>
       <c r="B33" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136373218</v>
       </c>
       <c r="B34" t="n">
-        <v>101440</v>
+        <v>101453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>136373222</v>
       </c>
       <c r="B35" t="n">
-        <v>103623</v>
+        <v>103636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136373213</v>
       </c>
       <c r="B4" t="n">
-        <v>92901</v>
+        <v>92902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136373236</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>92902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136373238</v>
       </c>
       <c r="B10" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136373245</v>
       </c>
       <c r="B11" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>136373237</v>
       </c>
       <c r="B14" t="n">
-        <v>96644</v>
+        <v>96645</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>136373204</v>
       </c>
       <c r="B16" t="n">
-        <v>92662</v>
+        <v>92663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>136373239</v>
       </c>
       <c r="B20" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136373241</v>
       </c>
       <c r="B21" t="n">
-        <v>90080</v>
+        <v>90081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136373246</v>
       </c>
       <c r="B26" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136373200</v>
       </c>
       <c r="B29" t="n">
-        <v>102467</v>
+        <v>102468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136373207</v>
       </c>
       <c r="B30" t="n">
-        <v>98197</v>
+        <v>98198</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136373201</v>
       </c>
       <c r="B33" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136373218</v>
       </c>
       <c r="B34" t="n">
-        <v>101453</v>
+        <v>101454</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>136373222</v>
       </c>
       <c r="B35" t="n">
-        <v>103636</v>
+        <v>103637</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
